--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1956" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="259">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,8 +260,7 @@
     <t>Diagnos</t>
   </si>
   <si>
-    <t>De diagnoser som matchar begäran. En instans per diagnos.
-Kardinalitet: Valfri, lista.</t>
+    <t>De diagnoser som matchar begäran. En instans per diagnos.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -353,8 +352,7 @@
     <t>Dokumenthuvud (PatientSummaryHeader)</t>
   </si>
   <si>
-    <t>Innehåller basinformation om dokumentet (PatientSummaryHeaderType).
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller basinformation om dokumentet (PatientSummaryHeaderType).</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.id</t>
@@ -369,58 +367,60 @@
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.documentId</t>
   </si>
   <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivString
+</t>
+  </si>
+  <si>
     <t>Dokumentets identitet</t>
   </si>
   <si>
-    <t>Dokumentets identitet som är unik inom källsystemet.
-Kardinalitet: Obligatorisk.</t>
+    <t>Dokumentets identitet som är unik inom källsystemet.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.sourceSystemHSAId</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
+    <t>HSA-id för källsystem</t>
+  </si>
+  <si>
+    <t>HSA-id för det system som tillgängliggör informationen.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.documentTitle</t>
+  </si>
+  <si>
+    <t>Titel (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetDiagnosis skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.documentTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivTimeStamp
 </t>
   </si>
   <si>
-    <t>HSA-id för källsystem</t>
-  </si>
-  <si>
-    <t>HSA-id för det system som tillgängliggör informationen.
-Kardinalitet: Obligatorisk.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.documentTitle</t>
-  </si>
-  <si>
-    <t>Titel (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetDiagnosis skickar inte documentTitle. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.documentTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Tidpunkt (ej tillämpligt)</t>
+  </si>
+  <si>
+    <t>N/A — GetDiagnosis skickar inte documentTime. Elementet är 0..0 per TKB.
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.patientId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivPersonIdTypeHealthcondDescription2
 </t>
   </si>
   <si>
-    <t>Tidpunkt (ej tillämpligt)</t>
-  </si>
-  <si>
-    <t>N/A — GetDiagnosis skickar inte documentTime. Elementet är 0..0 per TKB.</t>
-  </si>
-  <si>
-    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.patientId</t>
-  </si>
-  <si>
     <t>Patientidentifierare</t>
   </si>
   <si>
     <t>Identifierare för patient. id = patientens identifierare (12 tecken).
-type = OID för typ av identifierare. För personnummer: 1.2.752.129.2.1.3.1.
-Kardinalitet: Obligatorisk.</t>
+type = OID för typ av identifierare. För personnummer: 1.2.752.129.2.1.3.1.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional</t>
@@ -429,8 +429,7 @@
     <t>Ansvarig hälso- och sjukvårdsperson</t>
   </si>
   <si>
-    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Information om den hälso- och sjukvårdsperson som är ansvarig för informationen.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.id</t>
@@ -449,7 +448,7 @@
   </si>
   <si>
     <t>Tidpunkt då informationen registrerades. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalHSAId</t>
@@ -458,8 +457,7 @@
     <t>Författarens HSA-id</t>
   </si>
   <si>
-    <t>Författarens HSA-id.
-Kardinalitet: Valfri.</t>
+    <t>Författarens HSA-id.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalName</t>
@@ -468,22 +466,20 @@
     <t>Namn på hälso- och sjukvårdspersonal</t>
   </si>
   <si>
-    <t>Namn på hälso- och sjukvårdspersonal. Om tillgängligt ska detta anges.
-Kardinalitet: Valfri.</t>
+    <t>Namn på hälso- och sjukvårdspersonal. Om tillgängligt ska detta anges.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalRoleCode</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivCVTypeHealthcondDescription2
 </t>
   </si>
   <si>
     <t>Befattning</t>
   </si>
   <si>
-    <t>Information om personens befattning.
-Kardinalitet: Valfri.</t>
+    <t>Information om personens befattning.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit</t>
@@ -492,8 +488,7 @@
     <t>Organisationsenhet</t>
   </si>
   <si>
-    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.
-Kardinalitet: Valfri.</t>
+    <t>Den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.id</t>
@@ -511,8 +506,7 @@
     <t>HSA-id för organisationsenhet</t>
   </si>
   <si>
-    <t>HSA-id för organisationsenhet.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
+    <t>HSA-id för organisationsenhet.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitName</t>
@@ -521,8 +515,43 @@
     <t>Namn på organisationsenhet</t>
   </si>
   <si>
-    <t>Namnet på den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.
-Kardinalitet: Obligatorisk (inom OrgUnitType).</t>
+    <t>Namnet på den organisation som hälso- och sjukvårdspersonalen är uppdragstagare i.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitTelecom</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Telefon till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitEmail</t>
+  </si>
+  <si>
+    <t>E-post till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Epost till organisationsenhet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitAddress</t>
+  </si>
+  <si>
+    <t>Postadress till organisationsenhet</t>
+  </si>
+  <si>
+    <t>Postadress för den organisation som författaren är uppdragstagare på.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalOrgUnit.orgUnitLocation</t>
+  </si>
+  <si>
+    <t>Plats för organisationsenhet</t>
+  </si>
+  <si>
+    <t>Text som anger namnet på plats eller ort för organisationens fysiska placering.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalCareUnitHSAId</t>
@@ -531,8 +560,7 @@
     <t>HSA-id för vårdenhet</t>
   </si>
   <si>
-    <t>HSA-id för vårdenhet. Se regel 1 i TKB.
-Kardinalitet: Valfri (villkorlig, se regel 1).</t>
+    <t>HSA-id för vårdenhet. Se regel 1 i TKB.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.accountableHealthcareProfessional.healthcareProfessionalCareGiverHSAId</t>
@@ -541,8 +569,7 @@
     <t>HSA-id för vårdgivare</t>
   </si>
   <si>
-    <t>HSA-id för vårdgivaren, som är vårdgivare för den vårdenhet där personalen verkar.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för vårdgivaren, som är vårdgivare för den vårdenhet där personalen verkar.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.legalAuthenticator</t>
@@ -551,8 +578,7 @@
     <t>Signerande person</t>
   </si>
   <si>
-    <t>Information om vem som signerat informationen i dokumentet.
-Kardinalitet: Valfri.</t>
+    <t>Information om vem som signerat informationen i dokumentet.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.legalAuthenticator.id</t>
@@ -571,7 +597,7 @@
   </si>
   <si>
     <t>Tidpunkt för signering. Format: YYYYMMDDhhmmss.
-Kardinalitet: Obligatorisk.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.legalAuthenticator.legalAuthenticatorHSAId</t>
@@ -580,8 +606,7 @@
     <t>HSA-id för signerande person</t>
   </si>
   <si>
-    <t>HSA-id för person som signerat dokumentet.
-Kardinalitet: Valfri.</t>
+    <t>HSA-id för person som signerat dokumentet.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.legalAuthenticator.legalAuthenticatorName</t>
@@ -590,22 +615,20 @@
     <t>Namn på signerande person</t>
   </si>
   <si>
-    <t>Namn i klartext för signerande person.
-Kardinalitet: Valfri.</t>
+    <t>Namn i klartext för signerande person.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.approvedForPatient</t>
   </si>
   <si>
-    <t xml:space="preserve">boolean
+    <t xml:space="preserve">https://fhir.inera.se/ig/ehds-tk/StructureDefinition/SEEHDSRivBoolean
 </t>
   </si>
   <si>
     <t>Godkänd för visning till patient</t>
   </si>
   <si>
-    <t>Anger om information får delas till patient.
-Kardinalitet: Obligatorisk.</t>
+    <t>Anger om information får delas till patient.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.careContactId</t>
@@ -614,8 +637,22 @@
     <t>Vårdkontakts-id</t>
   </si>
   <si>
-    <t>Identitet för den hälso- och sjukvårdskontakt som diagnosen dokumenterades vid.
-Kardinalitet: Valfri.</t>
+    <t>Identitet för den hälso- och sjukvårdskontakt som diagnosen dokumenterades vid.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.nullified</t>
+  </si>
+  <si>
+    <t>Makulerad</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisHeader.nullifiedReason</t>
+  </si>
+  <si>
+    <t>Makuleringsorsak</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody</t>
@@ -624,8 +661,7 @@
     <t>Diagnosens innehåll</t>
   </si>
   <si>
-    <t>DiagnosisBodyType — diagnosens informationsinnehåll.
-Kardinalitet: Obligatorisk.</t>
+    <t>DiagnosisBodyType — diagnosens informationsinnehåll.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.id</t>
@@ -644,7 +680,13 @@
   </si>
   <si>
     <t>Anges som HD (huvuddiagnos) eller BY (bidiagnos) från kv_diagnostyp. Se DiagnosisTypeCS/DiagnosisTypeVS.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: Huvuddiagnos, Bidiagnos.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.typeOfDiagnosis.value</t>
+  </si>
+  <si>
+    <t>Elementets textinnehåll</t>
   </si>
   <si>
     <t>required</t>
@@ -653,14 +695,16 @@
     <t>https://fhir.inera.se/ig/ehds-tk/ValueSet/diagnosistype-vs</t>
   </si>
   <si>
+    <t>SEEHDSRivString.value</t>
+  </si>
+  <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.chronicDiagnosis</t>
   </si>
   <si>
     <t>Kronisk diagnos</t>
   </si>
   <si>
-    <t>Sätts till true om diagnosen är kronisk, false om den inte är kronisk.
-Kardinalitet: Valfri.</t>
+    <t>Sätts till true om diagnosen är kronisk, false om den inte är kronisk.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.diagnosisTime</t>
@@ -670,7 +714,7 @@
   </si>
   <si>
     <t>Tidpunkt då bedömningen gjordes. Format: YYYYMMDDhhmmss.
-Kardinalitet: Valfri.</t>
+Format enligt XSD (TimeStampType): ÅÅÅÅMMDDttmmss.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.diagnosisCode</t>
@@ -679,8 +723,7 @@
     <t>Diagnoskod</t>
   </si>
   <si>
-    <t>Diagnoskod. Normalt ICD-10-SE (OID okänt — se ASSUME-001 i QUESTIONS.md).
-Kardinalitet: Valfri.</t>
+    <t>Diagnoskod. Normalt ICD-10-SE (OID okänt — se ASSUME-001 i QUESTIONS.md).</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.relatedDiagnosis</t>
@@ -689,8 +732,7 @@
     <t>Relaterad diagnos</t>
   </si>
   <si>
-    <t>Relaterad diagnos. Associationen används för att koppla en bidiagnos till sin huvuddiagnos.
-Kardinalitet: Valfri, lista.</t>
+    <t>Relaterad diagnos. Associationen används för att koppla en bidiagnos till sin huvuddiagnos.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.diagnosis.diagnosisBody.relatedDiagnosis.id</t>
@@ -708,8 +750,7 @@
     <t>Relaterad diagnos dokumentid</t>
   </si>
   <si>
-    <t>Unik identitet för den relaterade diagnosen.
-Kardinalitet: Obligatorisk.</t>
+    <t>Unik identitet för den relaterade diagnosen.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.result</t>
@@ -718,8 +759,7 @@
     <t>Resultat</t>
   </si>
   <si>
-    <t>Innehåller information om begäran gick bra eller ej.
-Kardinalitet: Obligatorisk.</t>
+    <t>Innehåller information om begäran gick bra eller ej.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.result.id</t>
@@ -734,15 +774,11 @@
     <t>SEEHDSLMDiagnosis.result.resultCode</t>
   </si>
   <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
     <t>Resultatkod</t>
   </si>
   <si>
     <t>Kan endast vara OK, INFO eller ERROR.
-Kardinalitet: Obligatorisk.</t>
+Tillåtna värden enligt XSD: OK, ERROR, INFO.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.result.errorCode</t>
@@ -752,7 +788,7 @@
   </si>
   <si>
     <t>Sätts endast om resultCode är ERROR. Tillåtna värden: INVALID_REQUEST.
-Kardinalitet: Valfri.</t>
+Tillåtna värden enligt XSD: INVALID_REQUEST.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.result.logId</t>
@@ -761,8 +797,16 @@
     <t>Log-id</t>
   </si>
   <si>
-    <t>En UUID som kan användas vid felanmälan för att spåra felet.
-Kardinalitet: Obligatorisk.</t>
+    <t>En UUID som kan användas vid felanmälan för att spåra felet.</t>
+  </si>
+  <si>
+    <t>SEEHDSLMDiagnosis.result.subCode</t>
+  </si>
+  <si>
+    <t>Subkod</t>
+  </si>
+  <si>
+    <t>Inga subkoder är specificerade.</t>
   </si>
   <si>
     <t>SEEHDSLMDiagnosis.result.message</t>
@@ -771,8 +815,7 @@
     <t>Meddelande</t>
   </si>
   <si>
-    <t>En beskrivande text som kan visas för användaren.
-Kardinalitet: Valfri.</t>
+    <t>En beskrivande text som kan visas för användaren.</t>
   </si>
 </sst>
 </file>
@@ -1074,7 +1117,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ61"/>
+  <dimension ref="A1:AJ69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="106.203125" customWidth="true" bestFit="true"/>
@@ -1087,7 +1130,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="15.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1108,7 +1151,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="102.48046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="104.44921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -2164,13 +2207,13 @@
         <v>72</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2238,10 +2281,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2264,7 +2307,7 @@
         <v>72</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>117</v>
@@ -2321,7 +2364,7 @@
         <v>72</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>83</v>
@@ -2364,7 +2407,7 @@
         <v>72</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s" s="2">
         <v>120</v>
@@ -2564,13 +2607,13 @@
         <v>72</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2638,10 +2681,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2667,10 +2710,10 @@
         <v>78</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2721,7 +2764,7 @@
         <v>72</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>83</v>
@@ -2738,10 +2781,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2838,10 +2881,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2940,10 +2983,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3044,10 +3087,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3073,10 +3116,10 @@
         <v>123</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3127,7 +3170,7 @@
         <v>72</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>83</v>
@@ -3144,10 +3187,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3170,13 +3213,13 @@
         <v>72</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3227,7 +3270,7 @@
         <v>72</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>73</v>
@@ -3244,10 +3287,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3270,13 +3313,13 @@
         <v>72</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3327,7 +3370,7 @@
         <v>72</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>73</v>
@@ -3344,10 +3387,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3370,13 +3413,13 @@
         <v>72</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3427,7 +3470,7 @@
         <v>72</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>73</v>
@@ -3444,10 +3487,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3473,10 +3516,10 @@
         <v>78</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3527,7 +3570,7 @@
         <v>72</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>73</v>
@@ -3544,10 +3587,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3644,10 +3687,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3746,10 +3789,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3850,10 +3893,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3876,13 +3919,13 @@
         <v>72</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3933,7 +3976,7 @@
         <v>72</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -3950,10 +3993,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3976,13 +4019,13 @@
         <v>72</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4033,7 +4076,7 @@
         <v>72</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -4050,10 +4093,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4076,13 +4119,13 @@
         <v>72</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4133,7 +4176,7 @@
         <v>72</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>73</v>
@@ -4150,10 +4193,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4176,13 +4219,13 @@
         <v>72</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4233,7 +4276,7 @@
         <v>72</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>73</v>
@@ -4250,10 +4293,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4276,13 +4319,13 @@
         <v>72</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4333,7 +4376,7 @@
         <v>72</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>73</v>
@@ -4345,15 +4388,15 @@
         <v>72</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4376,13 +4419,13 @@
         <v>72</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>86</v>
+        <v>172</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4433,7 +4476,7 @@
         <v>72</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>87</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>73</v>
@@ -4450,21 +4493,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>72</v>
@@ -4476,17 +4519,15 @@
         <v>72</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>72</v>
@@ -4523,75 +4564,71 @@
         <v>72</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>72</v>
       </c>
@@ -4639,27 +4676,27 @@
         <v>72</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4667,7 +4704,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>83</v>
@@ -4682,13 +4719,13 @@
         <v>72</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4739,10 +4776,10 @@
         <v>72</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>83</v>
@@ -4751,15 +4788,15 @@
         <v>72</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4782,13 +4819,13 @@
         <v>72</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>86</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4839,7 +4876,7 @@
         <v>72</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>87</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>73</v>
@@ -4856,21 +4893,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>72</v>
@@ -4882,15 +4919,17 @@
         <v>72</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>72</v>
@@ -4927,71 +4966,75 @@
         <v>72</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>90</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>183</v>
+        <v>102</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>72</v>
       </c>
@@ -5039,19 +5082,19 @@
         <v>72</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40">
@@ -5067,7 +5110,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>83</v>
@@ -5082,7 +5125,7 @@
         <v>72</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>186</v>
@@ -5142,7 +5185,7 @@
         <v>185</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>83</v>
@@ -5167,7 +5210,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>83</v>
@@ -5182,7 +5225,7 @@
         <v>72</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>189</v>
@@ -5242,7 +5285,7 @@
         <v>188</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>83</v>
@@ -5251,7 +5294,7 @@
         <v>72</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
@@ -5282,13 +5325,13 @@
         <v>72</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>85</v>
+        <v>192</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>86</v>
+        <v>193</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5339,7 +5382,7 @@
         <v>72</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>73</v>
@@ -5356,21 +5399,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>72</v>
@@ -5382,17 +5425,15 @@
         <v>72</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>91</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>72</v>
@@ -5429,75 +5470,71 @@
         <v>72</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>102</v>
+        <v>199</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>72</v>
       </c>
@@ -5545,27 +5582,27 @@
         <v>72</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>105</v>
+        <v>198</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5573,10 +5610,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>72</v>
@@ -5588,13 +5625,13 @@
         <v>72</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5621,11 +5658,13 @@
         <v>72</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>72</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>72</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>198</v>
+        <v>72</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>72</v>
@@ -5643,13 +5682,13 @@
         <v>72</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>72</v>
@@ -5660,10 +5699,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5674,7 +5713,7 @@
         <v>73</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>72</v>
@@ -5686,13 +5725,13 @@
         <v>72</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>182</v>
+        <v>113</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5743,13 +5782,13 @@
         <v>72</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>72</v>
@@ -5760,10 +5799,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5771,7 +5810,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>83</v>
@@ -5786,13 +5825,13 @@
         <v>72</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5843,10 +5882,10 @@
         <v>72</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>83</v>
@@ -5855,15 +5894,15 @@
         <v>72</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5886,13 +5925,13 @@
         <v>72</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>207</v>
+        <v>86</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5943,7 +5982,7 @@
         <v>72</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>205</v>
+        <v>87</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>73</v>
@@ -5960,14 +5999,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -5986,15 +6025,17 @@
         <v>72</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>72</v>
@@ -6031,19 +6072,19 @@
         <v>72</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>208</v>
+        <v>97</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>73</v>
@@ -6055,7 +6096,7 @@
         <v>72</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>81</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
@@ -6067,35 +6108,39 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>72</v>
       </c>
@@ -6143,19 +6188,19 @@
         <v>72</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
@@ -6167,14 +6212,14 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>72</v>
@@ -6186,17 +6231,15 @@
         <v>72</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>91</v>
+        <v>213</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>72</v>
@@ -6233,75 +6276,71 @@
         <v>72</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>97</v>
+        <v>212</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>102</v>
+        <v>216</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>72</v>
       </c>
@@ -6325,13 +6364,11 @@
         <v>72</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>72</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>72</v>
+        <v>218</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>72</v>
@@ -6349,27 +6386,27 @@
         <v>72</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>105</v>
+        <v>219</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6377,7 +6414,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>83</v>
@@ -6392,13 +6429,13 @@
         <v>72</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6449,10 +6486,10 @@
         <v>72</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>83</v>
@@ -6466,10 +6503,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6477,7 +6514,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>83</v>
@@ -6492,13 +6529,13 @@
         <v>72</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6549,10 +6586,10 @@
         <v>72</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>83</v>
@@ -6561,15 +6598,15 @@
         <v>72</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6592,13 +6629,13 @@
         <v>72</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>85</v>
+        <v>227</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>86</v>
+        <v>228</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6649,7 +6686,7 @@
         <v>72</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>87</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>73</v>
@@ -6666,14 +6703,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -6692,17 +6729,15 @@
         <v>72</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>91</v>
+        <v>230</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>93</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>72</v>
@@ -6739,19 +6774,19 @@
         <v>72</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>73</v>
@@ -6763,51 +6798,47 @@
         <v>72</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>104</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>72</v>
       </c>
@@ -6855,38 +6886,38 @@
         <v>72</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>98</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>72</v>
@@ -6898,15 +6929,17 @@
         <v>72</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>224</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>72</v>
@@ -6943,71 +6976,75 @@
         <v>72</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>223</v>
+        <v>97</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>224</v>
+        <v>90</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>228</v>
+        <v>102</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>104</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>72</v>
       </c>
@@ -7055,27 +7092,27 @@
         <v>72</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>227</v>
+        <v>105</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>72</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7098,13 +7135,13 @@
         <v>72</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7155,7 +7192,7 @@
         <v>72</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -7172,10 +7209,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7183,7 +7220,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>83</v>
@@ -7198,13 +7235,13 @@
         <v>72</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7255,10 +7292,10 @@
         <v>72</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>83</v>
@@ -7267,6 +7304,812 @@
         <v>72</v>
       </c>
       <c r="AJ61" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
         <v>72</v>
       </c>
     </row>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMDiagnosis.xlsx
+++ b/StructureDefinition-SEEHDSLMDiagnosis.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
